--- a/lib/davinci_pas_test_kit/requirements/hl7.fhir.us.davinci-pas_2.2.1_requirements.xlsx
+++ b/lib/davinci_pas_test_kit/requirements/hl7.fhir.us.davinci-pas_2.2.1_requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-pas-test-kit/lib/davinci_pas_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8115E68B-45AF-3F43-9D3B-81B26D0AE85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECB3255-5701-D742-A5D1-E246EC744CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="453">
   <si>
     <r>
       <rPr>
@@ -2733,6 +2733,24 @@
   </si>
   <si>
     <t>Updated actor - Client is responsible for the Claim</t>
+  </si>
+  <si>
+    <t>Data Sources **SHALL** be capable of populating the data element when sharing resources compliant with the profile.</t>
+  </si>
+  <si>
+    <t>hrex-conf-1</t>
+  </si>
+  <si>
+    <t>https://hl7.org/fhir/us/davinci-hrex/1.2.0/en/conformance.html#ci-c-conf-1</t>
+  </si>
+  <si>
+    <t>hrex-conf-2</t>
+  </si>
+  <si>
+    <t>Data Consumers **SHALL** be capable of processing resource instances containing the data elements without generating an error or causing the application to fail.</t>
+  </si>
+  <si>
+    <t>https://hl7.org/fhir/us/davinci-hrex/1.2.0/en/conformance.html#ci-c-conf-2</t>
   </si>
 </sst>
 </file>
@@ -6571,12 +6589,46 @@
       </c>
       <c r="R120" s="10"/>
     </row>
-    <row r="121" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B121" s="11"/>
+    <row r="121" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="A121" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="G121" s="7" t="b">
+        <v>0</v>
+      </c>
       <c r="R121" s="10"/>
     </row>
-    <row r="122" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B122" s="11"/>
+    <row r="122" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+      <c r="A122" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="G122" s="7" t="b">
+        <v>0</v>
+      </c>
       <c r="R122" s="10"/>
     </row>
     <row r="123" spans="1:21" ht="16" x14ac:dyDescent="0.2">
@@ -8557,6 +8609,8 @@
     <hyperlink ref="B52" r:id="rId3" location="ci-c-spec-11" xr:uid="{4E0F9A5A-0897-2C4B-98E8-127D0E73D6C1}"/>
     <hyperlink ref="B106" r:id="rId4" location="ci-c-spec-65" xr:uid="{2C76CA9A-AF34-C946-9996-4CD6012F10C0}"/>
     <hyperlink ref="B67" r:id="rId5" location="ci-c-spec-26" xr:uid="{2791CF85-461B-1340-B643-634665A3629B}"/>
+    <hyperlink ref="B121" r:id="rId6" location="ci-c-conf-1" xr:uid="{F9502762-2CAC-054B-AC35-8FE364937A33}"/>
+    <hyperlink ref="B122" r:id="rId7" location="ci-c-conf-2" xr:uid="{B9020D2D-CDEC-9B45-9DBE-D41FF8F58455}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -8818,6 +8872,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -9071,7 +9134,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
@@ -9084,16 +9147,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12FB330C-B068-4EE3-928A-A72A297ABA91}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9113,7 +9175,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -9129,12 +9191,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/lib/davinci_pas_test_kit/requirements/hl7.fhir.us.davinci-pas_2.2.1_requirements.xlsx
+++ b/lib/davinci_pas_test_kit/requirements/hl7.fhir.us.davinci-pas_2.2.1_requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karlnaden/GlenViewAssociates/Inferno/source/davinci-pas-test-kit/lib/davinci_pas_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECB3255-5701-D742-A5D1-E246EC744CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CBA5F8-87A9-6243-B34C-A55BA7868568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20100" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Column Data" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$AI$340</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Requirements!$A$1:$AI$345</definedName>
     <definedName name="EXPLODE" localSheetId="0">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="EXPLODE">_xlfn.LAMBDA(_xlpm.string,_xlfn.MAKEARRAY(1,LEN(_xlpm.string),_xlfn.LAMBDA(_xlpm.r,_xlpm.c,MID(_xlpm.string,_xlpm.c,1))))</definedName>
     <definedName name="FIND_DUPLICATES" localSheetId="0">_xlfn.LAMBDA(_xlpm.test_word,_xlpm.test_key,_xlpm.words,_xlpm.keys,_xlpm.threshold, _xlfn.LET(_xlpm.duplist,_xlfn._xlws.FILTER(_xlpm.keys,_xlfn.BYROW(_xlpm.words, _xlfn.LAMBDA(_xlpm.word, Info!HAMDIST(INDEX(_xlpm.word,1,1), _xlpm.test_word)&lt;_xlpm.threshold))),_xlfn.SINGLE(_xlfn._xlws.FILTER(_xlpm.duplist,_xlpm.duplist&lt;&gt;_xlpm.test_key,""))))</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="459">
   <si>
     <r>
       <rPr>
@@ -1743,9 +1743,6 @@
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/conformance.html#ci-c-conf-15</t>
   </si>
   <si>
-    <t>conf-16</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/conformance.html#ci-c-conf-16</t>
   </si>
   <si>
@@ -1761,9 +1758,6 @@
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/metrics.html#ci-c-metric-2</t>
   </si>
   <si>
-    <t>priv-1</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/privacy.html#ci-c-priv-1</t>
   </si>
   <si>
@@ -1773,9 +1767,6 @@
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/privacy.html#ci-c-priv-2</t>
   </si>
   <si>
-    <t>priv-3</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/privacy.html#ci-c-priv-3</t>
   </si>
   <si>
@@ -1989,15 +1980,9 @@
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/specification.html#ci-c-spec-23</t>
   </si>
   <si>
-    <t>spec-24</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/specification.html#ci-c-spec-24</t>
   </si>
   <si>
-    <t>spec-25</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/davinci-pas/2.2.1/en/specification.html#ci-c-spec-25</t>
   </si>
   <si>
@@ -2391,24 +2376,15 @@
     <t>PAS clients and services **SHALL** use standard PAS data elements (i.e. elements found within PAS-defined or inherited profiles and marked as mandatory or mustSupport) to communicate needed data if such elements are intended to convey such information.</t>
   </si>
   <si>
-    <t>PAS implementing organizations **SHALL NOT** publish guidance setting expectations for where certain data elements are conveyed within PAS and inherited data structures, but **MAY** submit change requests to PAS, HRex, or US Core requesting that additional guidance be provided to implementers on data structure usage to increase consistency across implementations.</t>
-  </si>
-  <si>
     <t>Each of these IGs recommends a set of metrics that **SHOULD** or **MAY** be collected by their respective implementations to facilitate the evaluation of adoption, functionality, processes, and improved outcomes.</t>
   </si>
   <si>
     <t>PAS implementers **SHOULD** store information for each PAS call in a manner that would allow them to respond to measures based on this logical model.</t>
   </si>
   <si>
-    <t>Implementations **SHALL** permit provider review of data prior to transmission, but **SHALL NOT** require such review.</t>
-  </si>
-  <si>
     <t>Payers who do not view the FHIR version of the transmitted information **SHOULD** be aware of the possibility of these limitations and ensure they have policies that enforce appropriate sharing constraints on data.</t>
   </si>
   <si>
-    <t>PAS Servers **SHOULD** support server-server OAuth and **MAY** support mutually authenticated TLS.</t>
-  </si>
-  <si>
     <t>Timings **SHALL** have at least one of: a count, a frequency and period and periodUnit (with optional frequencyMax and periodMax), a calendarPattern, or a deliveryPattern.</t>
   </si>
   <si>
@@ -2505,12 +2481,6 @@
     <t>All resources **SHALL** comply with their respective profiles.</t>
   </si>
   <si>
-    <t>FHIR elements not marked as 'must support' **MAY** be included in resources within the Bundle, but client systems **SHOULD** have no expectation of such elements being processed by the payer unless prior arrangements have been made.</t>
-  </si>
-  <si>
-    <t>Systems that do not process such elements **SHALL** ignore unsupported elements unless they are 'modifier' elements, in which case the system **MAY** treat the presence of the element as an error.</t>
-  </si>
-  <si>
     <t>In addition, the system **SHALL** make the entire PAS FHIR Bundle available to the intended payer.</t>
   </si>
   <si>
@@ -2650,18 +2620,6 @@
   </si>
   <si>
     <t>All exchanges **SHOULD** meet Federal and state regulations, including any HIPAA restrictions and restrictions on sensitive data.</t>
-  </si>
-  <si>
-    <t>SHALL NOT / MAY</t>
-  </si>
-  <si>
-    <t>SHOULD / MAY</t>
-  </si>
-  <si>
-    <t>SHALL NOT / SHALL</t>
-  </si>
-  <si>
-    <t>SHALL / MAY</t>
   </si>
   <si>
     <t>PAS Payer</t>
@@ -2751,6 +2709,66 @@
   </si>
   <si>
     <t>https://hl7.org/fhir/us/davinci-hrex/1.2.0/en/conformance.html#ci-c-conf-2</t>
+  </si>
+  <si>
+    <t>conf-16-A</t>
+  </si>
+  <si>
+    <t>PAS implementing organizations **SHALL NOT** publish guidance setting expectations for where certain data elements are conveyed within PAS and inherited data structures</t>
+  </si>
+  <si>
+    <t>PAS implementing organizations ... **MAY** submit change requests to PAS, HRex, or US Core requesting that additional guidance be provided to implementers on data structure usage to increase consistency across implementations.</t>
+  </si>
+  <si>
+    <t>conf-16-B</t>
+  </si>
+  <si>
+    <t>priv-1-A</t>
+  </si>
+  <si>
+    <t>priv-1-B</t>
+  </si>
+  <si>
+    <t>Implementations **SHALL** permit provider review of data prior to transmission</t>
+  </si>
+  <si>
+    <t>Implementations ... **SHALL NOT** require [provider review of data prior to transmission]</t>
+  </si>
+  <si>
+    <t>spec-25-A</t>
+  </si>
+  <si>
+    <t>Systems that do not process such elements **SHALL** ignore unsupported elements unless they are 'modifier' elements</t>
+  </si>
+  <si>
+    <t>[T]the system **MAY** treat the presence of the [unsupported 'modifier'] element as an error.</t>
+  </si>
+  <si>
+    <t>spec-25-B</t>
+  </si>
+  <si>
+    <t>priv-3-A</t>
+  </si>
+  <si>
+    <t>priv-3-B</t>
+  </si>
+  <si>
+    <t>PAS Servers **SHOULD** support server-server Oauth</t>
+  </si>
+  <si>
+    <t>PAS Servers ... **MAY** support mutually authenticated TLS.</t>
+  </si>
+  <si>
+    <t>spec-24-A</t>
+  </si>
+  <si>
+    <t>spec-24-B</t>
+  </si>
+  <si>
+    <t>FHIR elements not marked as 'must support' **MAY** be included in resources within the Bundle</t>
+  </si>
+  <si>
+    <t>[C]lient systems **SHOULD** have no expectation of such [non 'must support'] elements being processed by the payer unless prior arrangements have been made.</t>
   </si>
 </sst>
 </file>
@@ -3687,7 +3705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}">
-  <dimension ref="A1:AI340"/>
+  <dimension ref="A1:AI345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="7"/>
@@ -3770,7 +3788,7 @@
         <v>23</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>24</v>
@@ -3788,19 +3806,19 @@
         <v>74</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G2" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P2" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R2" s="10"/>
       <c r="Y2" s="13"/>
@@ -3822,19 +3840,19 @@
         <v>76</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G3" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R3" s="10"/>
       <c r="Y3" s="13"/>
@@ -3853,19 +3871,19 @@
         <v>78</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G4" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R4" s="10"/>
       <c r="Y4" s="13"/>
@@ -3884,22 +3902,22 @@
         <v>80</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G5" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="Y5" s="13"/>
       <c r="Z5" s="5"/>
@@ -3917,19 +3935,19 @@
         <v>82</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R6" s="10"/>
       <c r="Y6" s="13"/>
@@ -3948,22 +3966,22 @@
         <v>84</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G7" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="X7" s="14"/>
       <c r="Y7" s="13"/>
@@ -3982,22 +4000,22 @@
         <v>86</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G8" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R8" s="16" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="68" x14ac:dyDescent="0.2">
@@ -4008,13 +4026,13 @@
         <v>88</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G9" s="7" t="b">
         <v>0</v>
@@ -4029,13 +4047,13 @@
         <v>90</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>0</v>
@@ -4050,13 +4068,13 @@
         <v>92</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G11" s="7" t="b">
         <v>0</v>
@@ -4071,13 +4089,13 @@
         <v>94</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G12" s="7" t="b">
         <v>0</v>
@@ -4092,13 +4110,13 @@
         <v>96</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G13" s="7" t="b">
         <v>0</v>
@@ -4113,13 +4131,13 @@
         <v>98</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G14" s="7" t="b">
         <v>0</v>
@@ -4134,22 +4152,22 @@
         <v>100</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G15" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R15" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:35" ht="51" x14ac:dyDescent="0.2">
@@ -4160,22 +4178,22 @@
         <v>102</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G16" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R16" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="51" x14ac:dyDescent="0.2">
@@ -4186,13 +4204,13 @@
         <v>104</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G17" s="7" t="b">
         <v>0</v>
@@ -4207,13 +4225,13 @@
         <v>106</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G18" s="7" t="b">
         <v>0</v>
@@ -4228,13 +4246,13 @@
         <v>108</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G19" s="7" t="b">
         <v>0</v>
@@ -4249,13 +4267,13 @@
         <v>110</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G20" s="7" t="b">
         <v>0</v>
@@ -4270,13 +4288,13 @@
         <v>112</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="G21" s="7" t="b">
         <v>0</v>
@@ -4290,22 +4308,22 @@
         <v>114</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="G22" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R22" s="16" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="102" x14ac:dyDescent="0.2">
@@ -4316,1176 +4334,1187 @@
         <v>116</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="G23" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R23" s="16" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="S23" s="10" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" ht="136" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
+      <c r="B24" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>118</v>
-      </c>
       <c r="C24" s="8" t="s">
-        <v>333</v>
+        <v>440</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" s="16" t="s">
         <v>420</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="G24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="16" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="G25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="R25" s="10"/>
-    </row>
-    <row r="26" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>122</v>
-      </c>
       <c r="C26" s="8" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="G26" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="R26" s="10"/>
     </row>
-    <row r="27" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="R27" s="10"/>
+    </row>
+    <row r="28" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G28" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="R28" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="S28" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G29" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="R29" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="S29" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B30" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="G27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="R27" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="S27" s="10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="85" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="C30" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="G28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="R28" s="10"/>
-    </row>
-    <row r="29" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="G29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="R29" s="10"/>
-    </row>
-    <row r="30" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="E30" s="7" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="G30" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P30" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="R30" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S30" s="10" t="s">
-        <v>438</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>131</v>
+        <v>451</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>340</v>
+        <v>453</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G31" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="R31" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S31" s="10" t="s">
-        <v>438</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>133</v>
+        <v>452</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>341</v>
+        <v>454</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G32" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R32" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S32" s="10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="170" x14ac:dyDescent="0.2">
+      <c r="P32" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="R32" s="10"/>
+    </row>
+    <row r="33" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G33" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R33" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S33" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" ht="119" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="G34" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P34" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R34" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S34" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="136" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="G35" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="P35" s="10" t="s">
-        <v>428</v>
-      </c>
       <c r="R35" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S35" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="170" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G36" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R36" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S36" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="119" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G37" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R37" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S37" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G38" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P38" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R38" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="G39" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R39" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S39" s="10" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="G40" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R40" s="10"/>
+      <c r="P40" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="R40" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S40" s="10" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="41" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="G41" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R41" s="10"/>
+      <c r="P41" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="R41" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S41" s="10" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="42" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="G42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P42" s="10" t="s">
+        <v>414</v>
       </c>
       <c r="R42" s="16" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="S42" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G43" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" s="10"/>
     </row>
-    <row r="44" spans="1:19" ht="136" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G44" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" s="10"/>
     </row>
-    <row r="45" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="G45" s="7" t="b">
         <v>1</v>
       </c>
       <c r="R45" s="16" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="S45" s="10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G46" s="7" t="b">
         <v>1</v>
       </c>
       <c r="R46" s="10"/>
     </row>
-    <row r="47" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" ht="136" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G47" s="7" t="b">
         <v>1</v>
       </c>
       <c r="R47" s="10"/>
     </row>
-    <row r="48" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E48" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G48" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="S48" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="G48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R48" s="10"/>
-    </row>
-    <row r="49" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="G49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R49" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S49" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="R49" s="10"/>
+    </row>
+    <row r="50" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="G50" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="10"/>
     </row>
-    <row r="51" spans="1:19" ht="153" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G51" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R51" s="10"/>
     </row>
-    <row r="52" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="G52" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R52" s="10" t="s">
-        <v>442</v>
+      <c r="R52" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S52" s="10" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="G53" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R53" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+      <c r="R53" s="10"/>
+    </row>
+    <row r="54" spans="1:19" ht="153" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G54" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R54" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R54" s="10"/>
+    </row>
+    <row r="55" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G55" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G56" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R56" s="10"/>
-    </row>
-    <row r="57" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="R56" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>443</v>
+        <v>354</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G57" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R57" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G58" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R58" s="10" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G59" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R59" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+      <c r="R59" s="10"/>
+    </row>
+    <row r="60" spans="1:19" ht="85" x14ac:dyDescent="0.2">
       <c r="A60" s="7" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>367</v>
+        <v>429</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G60" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R60" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="102" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G61" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R61" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G62" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R62" s="10"/>
-    </row>
-    <row r="63" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+      <c r="R62" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G63" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R63" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G64" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R64" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" ht="102" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>421</v>
+        <v>31</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G65" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R65" s="10"/>
     </row>
-    <row r="66" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>372</v>
+        <v>36</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>423</v>
+        <v>26</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G66" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R66" s="10"/>
-    </row>
-    <row r="67" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="R66" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G67" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="U67" s="16" t="s">
-        <v>445</v>
+      <c r="R67" s="10" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A68" s="7" t="s">
-        <v>205</v>
+        <v>455</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>374</v>
+        <v>457</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G68" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R68" s="10"/>
     </row>
-    <row r="69" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
-        <v>207</v>
+        <v>456</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>375</v>
+        <v>458</v>
       </c>
       <c r="D69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G69" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R69" s="10"/>
+    </row>
+    <row r="70" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="A70" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="G69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R69" s="10"/>
-    </row>
-    <row r="70" spans="1:21" ht="119" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="E70" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G70" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R70" s="10"/>
     </row>
-    <row r="71" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="s">
-        <v>211</v>
+        <v>450</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G71" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R71" s="10"/>
     </row>
-    <row r="72" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>363</v>
@@ -5494,28 +5523,30 @@
         <v>26</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G72" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R72" s="10"/>
-    </row>
-    <row r="73" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+      <c r="U72" s="16" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>364</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G73" s="7" t="b">
         <v>0</v>
@@ -5524,40 +5555,40 @@
     </row>
     <row r="74" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A74" s="7" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G74" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R74" s="10"/>
     </row>
-    <row r="75" spans="1:21" ht="102" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" ht="119" x14ac:dyDescent="0.2">
       <c r="A75" s="7" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G75" s="7" t="b">
         <v>0</v>
@@ -5566,468 +5597,467 @@
     </row>
     <row r="76" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A76" s="7" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G76" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="U76" s="16" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+      <c r="R76" s="10"/>
+    </row>
+    <row r="77" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A77" s="7" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G77" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R77" s="10"/>
     </row>
-    <row r="78" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="D78" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G78" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R78" s="10"/>
+    </row>
+    <row r="79" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+      <c r="A79" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D79" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="G78" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R78" s="10"/>
-    </row>
-    <row r="79" spans="1:21" ht="68" x14ac:dyDescent="0.2">
-      <c r="A79" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="E79" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G79" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R79" s="10"/>
     </row>
-    <row r="80" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" ht="102" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D80" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G80" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R80" s="10"/>
     </row>
-    <row r="81" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="D81" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G81" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U81" s="16" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+      <c r="A82" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G82" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R82" s="10"/>
+    </row>
+    <row r="83" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+      <c r="A83" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G83" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R83" s="10"/>
+    </row>
+    <row r="84" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+      <c r="A84" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="G81" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R81" s="10"/>
-    </row>
-    <row r="82" spans="1:19" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="G82" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R82" s="10"/>
-    </row>
-    <row r="83" spans="1:19" ht="68" x14ac:dyDescent="0.2">
-      <c r="A83" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="G83" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R83" s="10"/>
-    </row>
-    <row r="84" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A84" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="E84" s="7" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G84" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R84" s="10"/>
     </row>
-    <row r="85" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="7" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G85" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R85" s="10"/>
     </row>
-    <row r="86" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="G86" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R86" s="10"/>
     </row>
-    <row r="87" spans="1:19" ht="68" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G87" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R87" s="10"/>
     </row>
-    <row r="88" spans="1:19" ht="136" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="G88" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R88" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="S88" s="10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+      <c r="R88" s="10"/>
+    </row>
+    <row r="89" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="7" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G89" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R89" s="10"/>
     </row>
-    <row r="90" spans="1:19" ht="136" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A90" s="7" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G90" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R90" s="10"/>
     </row>
-    <row r="91" spans="1:19" ht="102" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A91" s="7" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G91" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R91" s="10"/>
     </row>
-    <row r="92" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A92" s="7" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G92" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R92" s="10"/>
     </row>
-    <row r="93" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21" ht="136" x14ac:dyDescent="0.2">
       <c r="A93" s="7" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>38</v>
+        <v>382</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E93" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G93" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R93" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="S93" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="G93" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R93" s="10"/>
-    </row>
-    <row r="94" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A94" s="7" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G94" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R94" s="10"/>
     </row>
-    <row r="95" spans="1:19" ht="85" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21" ht="136" x14ac:dyDescent="0.2">
       <c r="A95" s="7" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G95" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R95" s="10"/>
     </row>
-    <row r="96" spans="1:19" ht="34" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21" ht="102" x14ac:dyDescent="0.2">
       <c r="A96" s="7" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="F96" s="29"/>
+        <v>410</v>
+      </c>
       <c r="G96" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R96" s="10"/>
     </row>
-    <row r="97" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G97" s="7" t="b">
         <v>0</v>
@@ -6036,629 +6066,714 @@
     </row>
     <row r="98" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A98" s="7" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>401</v>
+        <v>38</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G98" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R98" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+      <c r="R98" s="10"/>
+    </row>
+    <row r="99" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A99" s="7" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E99" s="12" t="s">
-        <v>424</v>
+      <c r="E99" s="7" t="s">
+        <v>410</v>
       </c>
       <c r="G99" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R99" s="10" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+      <c r="R99" s="10"/>
+    </row>
+    <row r="100" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A100" s="7" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G100" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R100" s="10"/>
     </row>
-    <row r="101" spans="1:21" ht="136" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" s="7" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>424</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="F101" s="29"/>
       <c r="G101" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R101" s="10"/>
     </row>
-    <row r="102" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A102" s="7" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="G102" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R102" s="10"/>
     </row>
-    <row r="103" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A103" s="7" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="D103" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G103" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R103" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S103" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+      <c r="R103" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A104" s="7" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>425</v>
+        <v>26</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>410</v>
       </c>
       <c r="G104" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R104" s="10"/>
-    </row>
-    <row r="105" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="R104" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A105" s="7" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G105" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R105" s="10"/>
     </row>
-    <row r="106" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:21" ht="136" x14ac:dyDescent="0.2">
       <c r="A106" s="7" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="D106" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="G106" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R106" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="U106" s="16" t="s">
-        <v>446</v>
-      </c>
+      <c r="R106" s="10"/>
     </row>
     <row r="107" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A107" s="7" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="C107" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D107" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>425</v>
-      </c>
       <c r="G107" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R107" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="U107" s="16" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+      <c r="R107" s="10"/>
+    </row>
+    <row r="108" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A108" s="7" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="G108" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R108" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="U108" s="16" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" ht="102" x14ac:dyDescent="0.2">
+      <c r="R108" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S108" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A109" s="7" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C109" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G109" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R109" s="10"/>
+    </row>
+    <row r="110" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="A110" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E110" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="D109" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="G109" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R109" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S109" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" ht="119" x14ac:dyDescent="0.2">
-      <c r="A110" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B110" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E110" s="42" t="s">
-        <v>426</v>
-      </c>
       <c r="G110" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R110" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S110" s="10" t="s">
-        <v>444</v>
-      </c>
+      <c r="R110" s="10"/>
     </row>
     <row r="111" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A111" s="7" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E111" s="42" t="s">
-        <v>426</v>
+      <c r="E111" s="7" t="s">
+        <v>411</v>
       </c>
       <c r="G111" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R111" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S111" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" ht="119" x14ac:dyDescent="0.2">
+      <c r="R111" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="U111" s="16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="7" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E112" s="42" t="s">
-        <v>426</v>
+        <v>35</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>411</v>
       </c>
       <c r="G112" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R112" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="S112" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="113" spans="1:21" ht="102" x14ac:dyDescent="0.2">
+      <c r="R112" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="U112" s="16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="7" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E113" s="42" t="s">
-        <v>425</v>
+      <c r="E113" s="7" t="s">
+        <v>411</v>
       </c>
       <c r="G113" s="7" t="b">
         <v>0</v>
       </c>
       <c r="R113" s="10" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="U113" s="16" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="114" spans="1:21" ht="85" x14ac:dyDescent="0.2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" ht="102" x14ac:dyDescent="0.2">
       <c r="A114" s="7" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>39</v>
+        <v>402</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E114" s="42" t="s">
-        <v>424</v>
+      <c r="E114" s="7" t="s">
+        <v>411</v>
       </c>
       <c r="G114" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="R114" s="10"/>
-    </row>
-    <row r="115" spans="1:21" ht="34" x14ac:dyDescent="0.2">
+      <c r="R114" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S114" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" ht="119" x14ac:dyDescent="0.2">
       <c r="A115" s="7" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="D115" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E115" s="42" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G115" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="P115" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="R115" s="10"/>
-    </row>
-    <row r="116" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+      <c r="R115" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S115" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" ht="51" x14ac:dyDescent="0.2">
       <c r="A116" s="7" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>28</v>
+        <v>404</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E116" s="42" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="G116" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="P116" s="10" t="s">
+      <c r="R116" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S116" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" ht="119" x14ac:dyDescent="0.2">
+      <c r="A117" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E117" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="G117" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R117" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="S117" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" ht="102" x14ac:dyDescent="0.2">
+      <c r="A118" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E118" s="42" t="s">
+        <v>411</v>
+      </c>
+      <c r="G118" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R118" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="R116" s="10"/>
-    </row>
-    <row r="117" spans="1:21" ht="85" x14ac:dyDescent="0.2">
-      <c r="A117" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B117" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="G117" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P117" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="R117" s="10"/>
-    </row>
-    <row r="118" spans="1:21" ht="51" x14ac:dyDescent="0.2">
-      <c r="A118" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B118" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="G118" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P118" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="R118" s="10"/>
-    </row>
-    <row r="119" spans="1:21" ht="170" x14ac:dyDescent="0.2">
+      <c r="U118" s="16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A119" s="7" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>418</v>
+        <v>39</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E119" s="7" t="s">
-        <v>425</v>
+      <c r="E119" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="G119" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="P119" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="R119" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="S119" s="10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="120" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="R119" s="10"/>
+    </row>
+    <row r="120" spans="1:21" ht="34" x14ac:dyDescent="0.2">
       <c r="A120" s="7" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>426</v>
+        <v>26</v>
+      </c>
+      <c r="E120" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="G120" s="7" t="b">
         <v>0</v>
       </c>
       <c r="P120" s="10" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="R120" s="10"/>
     </row>
-    <row r="121" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21" ht="68" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
-        <v>448</v>
+        <v>296</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>449</v>
+        <v>297</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>447</v>
+        <v>28</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E121" s="7" t="s">
-        <v>426</v>
+      <c r="E121" s="42" t="s">
+        <v>410</v>
       </c>
       <c r="G121" s="7" t="b">
         <v>0</v>
       </c>
+      <c r="P121" s="10" t="s">
+        <v>414</v>
+      </c>
       <c r="R121" s="10"/>
     </row>
-    <row r="122" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21" ht="85" x14ac:dyDescent="0.2">
       <c r="A122" s="7" t="s">
-        <v>450</v>
+        <v>298</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>452</v>
+        <v>299</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>451</v>
+        <v>29</v>
       </c>
       <c r="D122" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="G122" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P122" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="R122" s="10"/>
+    </row>
+    <row r="123" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="A123" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G123" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P123" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="R123" s="10"/>
+    </row>
+    <row r="124" spans="1:21" ht="170" x14ac:dyDescent="0.2">
+      <c r="A124" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D124" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E122" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="G122" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R122" s="10"/>
-    </row>
-    <row r="123" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B123" s="11"/>
-      <c r="I123" s="31"/>
-      <c r="J123" s="31"/>
-      <c r="K123" s="31"/>
-      <c r="L123" s="31"/>
-      <c r="Q123" s="10"/>
-      <c r="R123" s="10"/>
-    </row>
-    <row r="124" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B124" s="11"/>
-      <c r="E124" s="42"/>
-      <c r="R124" s="10"/>
-    </row>
-    <row r="125" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B125" s="11"/>
+      <c r="E124" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G124" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P124" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="R124" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="S124" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="A125" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G125" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P125" s="10" t="s">
+        <v>414</v>
+      </c>
       <c r="R125" s="10"/>
     </row>
-    <row r="126" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B126" s="11"/>
+    <row r="126" spans="1:21" ht="51" x14ac:dyDescent="0.2">
+      <c r="A126" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G126" s="7" t="b">
+        <v>0</v>
+      </c>
       <c r="R126" s="10"/>
     </row>
-    <row r="127" spans="1:21" ht="16" x14ac:dyDescent="0.2">
-      <c r="B127" s="11"/>
+    <row r="127" spans="1:21" ht="68" x14ac:dyDescent="0.2">
+      <c r="A127" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="G127" s="7" t="b">
+        <v>0</v>
+      </c>
       <c r="R127" s="10"/>
     </row>
     <row r="128" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B128" s="11"/>
+      <c r="I128" s="31"/>
+      <c r="J128" s="31"/>
+      <c r="K128" s="31"/>
+      <c r="L128" s="31"/>
+      <c r="Q128" s="10"/>
       <c r="R128" s="10"/>
     </row>
     <row r="129" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6668,22 +6783,18 @@
     </row>
     <row r="130" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B130" s="11"/>
-      <c r="E130" s="42"/>
       <c r="R130" s="10"/>
     </row>
     <row r="131" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B131" s="11"/>
-      <c r="E131" s="42"/>
       <c r="R131" s="10"/>
     </row>
     <row r="132" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B132" s="11"/>
-      <c r="E132" s="42"/>
       <c r="R132" s="10"/>
     </row>
     <row r="133" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B133" s="11"/>
-      <c r="E133" s="42"/>
       <c r="R133" s="10"/>
     </row>
     <row r="134" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6703,6 +6814,7 @@
     </row>
     <row r="137" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B137" s="11"/>
+      <c r="E137" s="42"/>
       <c r="R137" s="10"/>
     </row>
     <row r="138" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6717,6 +6829,7 @@
     </row>
     <row r="140" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B140" s="11"/>
+      <c r="E140" s="42"/>
       <c r="R140" s="10"/>
     </row>
     <row r="141" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6730,34 +6843,33 @@
     </row>
     <row r="143" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B143" s="11"/>
+      <c r="E143" s="42"/>
       <c r="R143" s="10"/>
     </row>
     <row r="144" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B144" s="11"/>
+      <c r="E144" s="42"/>
       <c r="R144" s="10"/>
     </row>
     <row r="145" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B145" s="11"/>
-      <c r="E145" s="42"/>
       <c r="R145" s="10"/>
     </row>
     <row r="146" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B146" s="11"/>
+      <c r="E146" s="42"/>
       <c r="R146" s="10"/>
     </row>
     <row r="147" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B147" s="11"/>
-      <c r="E147" s="42"/>
       <c r="R147" s="10"/>
     </row>
     <row r="148" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B148" s="11"/>
-      <c r="E148" s="42"/>
       <c r="R148" s="10"/>
     </row>
     <row r="149" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B149" s="11"/>
-      <c r="E149" s="42"/>
       <c r="R149" s="10"/>
     </row>
     <row r="150" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6767,7 +6879,6 @@
     </row>
     <row r="151" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B151" s="11"/>
-      <c r="E151" s="42"/>
       <c r="R151" s="10"/>
     </row>
     <row r="152" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6777,22 +6888,27 @@
     </row>
     <row r="153" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B153" s="11"/>
+      <c r="E153" s="42"/>
       <c r="R153" s="10"/>
     </row>
     <row r="154" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B154" s="11"/>
+      <c r="E154" s="42"/>
       <c r="R154" s="10"/>
     </row>
     <row r="155" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B155" s="11"/>
+      <c r="E155" s="42"/>
       <c r="R155" s="10"/>
     </row>
     <row r="156" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B156" s="11"/>
+      <c r="E156" s="42"/>
       <c r="R156" s="10"/>
     </row>
     <row r="157" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B157" s="11"/>
+      <c r="E157" s="42"/>
       <c r="R157" s="10"/>
     </row>
     <row r="158" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6869,27 +6985,22 @@
     </row>
     <row r="176" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B176" s="11"/>
-      <c r="E176" s="42"/>
       <c r="R176" s="10"/>
     </row>
     <row r="177" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B177" s="11"/>
-      <c r="E177" s="42"/>
       <c r="R177" s="10"/>
     </row>
     <row r="178" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B178" s="11"/>
-      <c r="E178" s="42"/>
       <c r="R178" s="10"/>
     </row>
     <row r="179" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B179" s="11"/>
-      <c r="E179" s="42"/>
       <c r="R179" s="10"/>
     </row>
     <row r="180" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B180" s="11"/>
-      <c r="E180" s="42"/>
       <c r="R180" s="10"/>
     </row>
     <row r="181" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6909,6 +7020,7 @@
     </row>
     <row r="184" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B184" s="11"/>
+      <c r="E184" s="42"/>
       <c r="R184" s="10"/>
     </row>
     <row r="185" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6918,23 +7030,26 @@
     </row>
     <row r="186" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B186" s="11"/>
+      <c r="E186" s="42"/>
       <c r="R186" s="10"/>
     </row>
     <row r="187" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B187" s="11"/>
+      <c r="E187" s="42"/>
       <c r="R187" s="10"/>
     </row>
     <row r="188" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B188" s="11"/>
+      <c r="E188" s="42"/>
       <c r="R188" s="10"/>
     </row>
     <row r="189" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B189" s="11"/>
-      <c r="E189" s="42"/>
       <c r="R189" s="10"/>
     </row>
     <row r="190" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B190" s="11"/>
+      <c r="E190" s="42"/>
       <c r="R190" s="10"/>
     </row>
     <row r="191" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6943,16 +7058,15 @@
     </row>
     <row r="192" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B192" s="11"/>
-      <c r="E192" s="42"/>
       <c r="R192" s="10"/>
     </row>
     <row r="193" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B193" s="11"/>
-      <c r="E193" s="42"/>
       <c r="R193" s="10"/>
     </row>
     <row r="194" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B194" s="11"/>
+      <c r="E194" s="42"/>
       <c r="R194" s="10"/>
     </row>
     <row r="195" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6965,6 +7079,7 @@
     </row>
     <row r="197" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B197" s="11"/>
+      <c r="E197" s="42"/>
       <c r="R197" s="10"/>
     </row>
     <row r="198" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -6990,6 +7105,7 @@
     </row>
     <row r="203" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B203" s="11"/>
+      <c r="E203" s="42"/>
       <c r="R203" s="10"/>
     </row>
     <row r="204" spans="2:18" ht="16" x14ac:dyDescent="0.2">
@@ -7010,138 +7126,43 @@
     </row>
     <row r="208" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="B208" s="11"/>
-      <c r="E208" s="42"/>
       <c r="R208" s="10"/>
     </row>
     <row r="209" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B209" s="11"/>
-      <c r="E209" s="42"/>
       <c r="R209" s="10"/>
     </row>
     <row r="210" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B210" s="11"/>
-      <c r="E210" s="42"/>
       <c r="R210" s="10"/>
     </row>
     <row r="211" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B211" s="11"/>
-      <c r="E211" s="42"/>
       <c r="R211" s="10"/>
     </row>
-    <row r="212" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A212" s="7"/>
+    <row r="212" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B212" s="11"/>
-      <c r="C212" s="8"/>
-      <c r="D212" s="8"/>
-      <c r="E212" s="8"/>
-      <c r="F212" s="8"/>
-      <c r="G212" s="8"/>
-      <c r="H212" s="16"/>
-      <c r="I212" s="30"/>
-      <c r="J212" s="30"/>
-      <c r="K212" s="30"/>
-      <c r="L212" s="30"/>
-      <c r="M212" s="43"/>
-      <c r="N212" s="43"/>
-      <c r="O212" s="16"/>
-      <c r="P212" s="16"/>
-      <c r="Q212" s="16"/>
-      <c r="R212" s="16"/>
-      <c r="S212" s="16"/>
-      <c r="T212" s="16"/>
-      <c r="U212" s="16"/>
-    </row>
-    <row r="213" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A213" s="7"/>
+      <c r="R212" s="10"/>
+    </row>
+    <row r="213" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B213" s="11"/>
-      <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
-      <c r="E213" s="8"/>
-      <c r="F213" s="8"/>
-      <c r="G213" s="8"/>
-      <c r="H213" s="16"/>
-      <c r="I213" s="30"/>
-      <c r="J213" s="30"/>
-      <c r="K213" s="30"/>
-      <c r="L213" s="30"/>
-      <c r="M213" s="43"/>
-      <c r="N213" s="43"/>
-      <c r="O213" s="16"/>
-      <c r="P213" s="16"/>
-      <c r="Q213" s="16"/>
-      <c r="R213" s="16"/>
-      <c r="S213" s="16"/>
-      <c r="T213" s="16"/>
-      <c r="U213" s="16"/>
-    </row>
-    <row r="214" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A214" s="7"/>
+      <c r="E213" s="42"/>
+      <c r="R213" s="10"/>
+    </row>
+    <row r="214" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B214" s="11"/>
-      <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
-      <c r="E214" s="8"/>
-      <c r="F214" s="8"/>
-      <c r="G214" s="8"/>
-      <c r="H214" s="16"/>
-      <c r="I214" s="30"/>
-      <c r="J214" s="30"/>
-      <c r="K214" s="30"/>
-      <c r="L214" s="30"/>
-      <c r="M214" s="43"/>
-      <c r="N214" s="43"/>
-      <c r="O214" s="16"/>
-      <c r="P214" s="16"/>
-      <c r="Q214" s="16"/>
-      <c r="R214" s="16"/>
-      <c r="S214" s="16"/>
-      <c r="T214" s="16"/>
-      <c r="U214" s="16"/>
-    </row>
-    <row r="215" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A215" s="7"/>
+      <c r="E214" s="42"/>
+      <c r="R214" s="10"/>
+    </row>
+    <row r="215" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B215" s="11"/>
-      <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
-      <c r="E215" s="8"/>
-      <c r="F215" s="8"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="16"/>
-      <c r="I215" s="30"/>
-      <c r="J215" s="30"/>
-      <c r="K215" s="30"/>
-      <c r="L215" s="30"/>
-      <c r="M215" s="43"/>
-      <c r="N215" s="43"/>
-      <c r="O215" s="16"/>
-      <c r="P215" s="16"/>
-      <c r="Q215" s="16"/>
-      <c r="R215" s="16"/>
-      <c r="S215" s="16"/>
-      <c r="T215" s="16"/>
-      <c r="U215" s="16"/>
-    </row>
-    <row r="216" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A216" s="7"/>
+      <c r="E215" s="42"/>
+      <c r="R215" s="10"/>
+    </row>
+    <row r="216" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B216" s="11"/>
-      <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
-      <c r="E216" s="8"/>
-      <c r="F216" s="8"/>
-      <c r="G216" s="8"/>
-      <c r="H216" s="16"/>
-      <c r="I216" s="30"/>
-      <c r="J216" s="30"/>
-      <c r="K216" s="30"/>
-      <c r="L216" s="30"/>
-      <c r="M216" s="43"/>
-      <c r="N216" s="43"/>
-      <c r="O216" s="16"/>
-      <c r="P216" s="16"/>
-      <c r="Q216" s="16"/>
-      <c r="R216" s="16"/>
-      <c r="S216" s="16"/>
-      <c r="T216" s="16"/>
-      <c r="U216" s="16"/>
+      <c r="E216" s="42"/>
+      <c r="R216" s="10"/>
     </row>
     <row r="217" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="7"/>
@@ -7304,67 +7325,122 @@
       <c r="T223" s="16"/>
       <c r="U223" s="16"/>
     </row>
-    <row r="224" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A224" s="7"/>
       <c r="B224" s="11"/>
-      <c r="M224" s="9" t="str" cm="1">
-        <f t="array" ref="M224">PAGE_NAME(B224)</f>
-        <v/>
-      </c>
-      <c r="N224" s="9" t="str" cm="1">
-        <f t="array" ref="N224">SECTION_NAME(B224)</f>
-        <v/>
-      </c>
-      <c r="R224" s="10"/>
-    </row>
-    <row r="225" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="C224" s="8"/>
+      <c r="D224" s="8"/>
+      <c r="E224" s="8"/>
+      <c r="F224" s="8"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="16"/>
+      <c r="I224" s="30"/>
+      <c r="J224" s="30"/>
+      <c r="K224" s="30"/>
+      <c r="L224" s="30"/>
+      <c r="M224" s="43"/>
+      <c r="N224" s="43"/>
+      <c r="O224" s="16"/>
+      <c r="P224" s="16"/>
+      <c r="Q224" s="16"/>
+      <c r="R224" s="16"/>
+      <c r="S224" s="16"/>
+      <c r="T224" s="16"/>
+      <c r="U224" s="16"/>
+    </row>
+    <row r="225" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A225" s="7"/>
       <c r="B225" s="11"/>
-      <c r="M225" s="9" t="str" cm="1">
-        <f t="array" ref="M225">PAGE_NAME(B225)</f>
-        <v/>
-      </c>
-      <c r="N225" s="9" t="str" cm="1">
-        <f t="array" ref="N225">SECTION_NAME(B225)</f>
-        <v/>
-      </c>
-      <c r="R225" s="10"/>
-    </row>
-    <row r="226" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="C225" s="8"/>
+      <c r="D225" s="8"/>
+      <c r="E225" s="8"/>
+      <c r="F225" s="8"/>
+      <c r="G225" s="8"/>
+      <c r="H225" s="16"/>
+      <c r="I225" s="30"/>
+      <c r="J225" s="30"/>
+      <c r="K225" s="30"/>
+      <c r="L225" s="30"/>
+      <c r="M225" s="43"/>
+      <c r="N225" s="43"/>
+      <c r="O225" s="16"/>
+      <c r="P225" s="16"/>
+      <c r="Q225" s="16"/>
+      <c r="R225" s="16"/>
+      <c r="S225" s="16"/>
+      <c r="T225" s="16"/>
+      <c r="U225" s="16"/>
+    </row>
+    <row r="226" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A226" s="7"/>
       <c r="B226" s="11"/>
-      <c r="M226" s="9" t="str" cm="1">
-        <f t="array" ref="M226">PAGE_NAME(B226)</f>
-        <v/>
-      </c>
-      <c r="N226" s="9" t="str" cm="1">
-        <f t="array" ref="N226">SECTION_NAME(B226)</f>
-        <v/>
-      </c>
-      <c r="R226" s="10"/>
-    </row>
-    <row r="227" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="C226" s="8"/>
+      <c r="D226" s="8"/>
+      <c r="E226" s="8"/>
+      <c r="F226" s="8"/>
+      <c r="G226" s="8"/>
+      <c r="H226" s="16"/>
+      <c r="I226" s="30"/>
+      <c r="J226" s="30"/>
+      <c r="K226" s="30"/>
+      <c r="L226" s="30"/>
+      <c r="M226" s="43"/>
+      <c r="N226" s="43"/>
+      <c r="O226" s="16"/>
+      <c r="P226" s="16"/>
+      <c r="Q226" s="16"/>
+      <c r="R226" s="16"/>
+      <c r="S226" s="16"/>
+      <c r="T226" s="16"/>
+      <c r="U226" s="16"/>
+    </row>
+    <row r="227" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A227" s="7"/>
       <c r="B227" s="11"/>
-      <c r="M227" s="9" t="str" cm="1">
-        <f t="array" ref="M227">PAGE_NAME(B227)</f>
-        <v/>
-      </c>
-      <c r="N227" s="9" t="str" cm="1">
-        <f t="array" ref="N227">SECTION_NAME(B227)</f>
-        <v/>
-      </c>
-      <c r="R227" s="10"/>
-    </row>
-    <row r="228" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="C227" s="8"/>
+      <c r="D227" s="8"/>
+      <c r="E227" s="8"/>
+      <c r="F227" s="8"/>
+      <c r="G227" s="8"/>
+      <c r="H227" s="16"/>
+      <c r="I227" s="30"/>
+      <c r="J227" s="30"/>
+      <c r="K227" s="30"/>
+      <c r="L227" s="30"/>
+      <c r="M227" s="43"/>
+      <c r="N227" s="43"/>
+      <c r="O227" s="16"/>
+      <c r="P227" s="16"/>
+      <c r="Q227" s="16"/>
+      <c r="R227" s="16"/>
+      <c r="S227" s="16"/>
+      <c r="T227" s="16"/>
+      <c r="U227" s="16"/>
+    </row>
+    <row r="228" spans="1:21" s="44" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A228" s="7"/>
       <c r="B228" s="11"/>
-      <c r="M228" s="9" t="str" cm="1">
-        <f t="array" ref="M228">PAGE_NAME(B228)</f>
-        <v/>
-      </c>
-      <c r="N228" s="9" t="str" cm="1">
-        <f t="array" ref="N228">SECTION_NAME(B228)</f>
-        <v/>
-      </c>
-      <c r="R228" s="10"/>
-    </row>
-    <row r="229" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="C228" s="8"/>
+      <c r="D228" s="8"/>
+      <c r="E228" s="8"/>
+      <c r="F228" s="8"/>
+      <c r="G228" s="8"/>
+      <c r="H228" s="16"/>
+      <c r="I228" s="30"/>
+      <c r="J228" s="30"/>
+      <c r="K228" s="30"/>
+      <c r="L228" s="30"/>
+      <c r="M228" s="43"/>
+      <c r="N228" s="43"/>
+      <c r="O228" s="16"/>
+      <c r="P228" s="16"/>
+      <c r="Q228" s="16"/>
+      <c r="R228" s="16"/>
+      <c r="S228" s="16"/>
+      <c r="T228" s="16"/>
+      <c r="U228" s="16"/>
+    </row>
+    <row r="229" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B229" s="11"/>
       <c r="M229" s="9" t="str" cm="1">
         <f t="array" ref="M229">PAGE_NAME(B229)</f>
@@ -7376,7 +7452,7 @@
       </c>
       <c r="R229" s="10"/>
     </row>
-    <row r="230" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B230" s="11"/>
       <c r="M230" s="9" t="str" cm="1">
         <f t="array" ref="M230">PAGE_NAME(B230)</f>
@@ -7388,7 +7464,7 @@
       </c>
       <c r="R230" s="10"/>
     </row>
-    <row r="231" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="B231" s="11"/>
       <c r="M231" s="9" t="str" cm="1">
         <f t="array" ref="M231">PAGE_NAME(B231)</f>
@@ -7400,7 +7476,8 @@
       </c>
       <c r="R231" s="10"/>
     </row>
-    <row r="232" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="B232" s="11"/>
       <c r="M232" s="9" t="str" cm="1">
         <f t="array" ref="M232">PAGE_NAME(B232)</f>
         <v/>
@@ -7411,7 +7488,8 @@
       </c>
       <c r="R232" s="10"/>
     </row>
-    <row r="233" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="B233" s="11"/>
       <c r="M233" s="9" t="str" cm="1">
         <f t="array" ref="M233">PAGE_NAME(B233)</f>
         <v/>
@@ -7422,7 +7500,8 @@
       </c>
       <c r="R233" s="10"/>
     </row>
-    <row r="234" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="B234" s="11"/>
       <c r="M234" s="9" t="str" cm="1">
         <f t="array" ref="M234">PAGE_NAME(B234)</f>
         <v/>
@@ -7433,7 +7512,8 @@
       </c>
       <c r="R234" s="10"/>
     </row>
-    <row r="235" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="B235" s="11"/>
       <c r="M235" s="9" t="str" cm="1">
         <f t="array" ref="M235">PAGE_NAME(B235)</f>
         <v/>
@@ -7444,7 +7524,8 @@
       </c>
       <c r="R235" s="10"/>
     </row>
-    <row r="236" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:21" ht="16" x14ac:dyDescent="0.2">
+      <c r="B236" s="11"/>
       <c r="M236" s="9" t="str" cm="1">
         <f t="array" ref="M236">PAGE_NAME(B236)</f>
         <v/>
@@ -7455,7 +7536,7 @@
       </c>
       <c r="R236" s="10"/>
     </row>
-    <row r="237" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="M237" s="9" t="str" cm="1">
         <f t="array" ref="M237">PAGE_NAME(B237)</f>
         <v/>
@@ -7466,7 +7547,7 @@
       </c>
       <c r="R237" s="10"/>
     </row>
-    <row r="238" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="M238" s="9" t="str" cm="1">
         <f t="array" ref="M238">PAGE_NAME(B238)</f>
         <v/>
@@ -7477,7 +7558,7 @@
       </c>
       <c r="R238" s="10"/>
     </row>
-    <row r="239" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="M239" s="9" t="str" cm="1">
         <f t="array" ref="M239">PAGE_NAME(B239)</f>
         <v/>
@@ -7488,7 +7569,7 @@
       </c>
       <c r="R239" s="10"/>
     </row>
-    <row r="240" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="M240" s="9" t="str" cm="1">
         <f t="array" ref="M240">PAGE_NAME(B240)</f>
         <v/>
@@ -7499,7 +7580,7 @@
       </c>
       <c r="R240" s="10"/>
     </row>
-    <row r="241" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M241" s="9" t="str" cm="1">
         <f t="array" ref="M241">PAGE_NAME(B241)</f>
         <v/>
@@ -7510,7 +7591,7 @@
       </c>
       <c r="R241" s="10"/>
     </row>
-    <row r="242" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="242" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M242" s="9" t="str" cm="1">
         <f t="array" ref="M242">PAGE_NAME(B242)</f>
         <v/>
@@ -7521,7 +7602,7 @@
       </c>
       <c r="R242" s="10"/>
     </row>
-    <row r="243" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="243" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M243" s="9" t="str" cm="1">
         <f t="array" ref="M243">PAGE_NAME(B243)</f>
         <v/>
@@ -7532,7 +7613,7 @@
       </c>
       <c r="R243" s="10"/>
     </row>
-    <row r="244" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M244" s="9" t="str" cm="1">
         <f t="array" ref="M244">PAGE_NAME(B244)</f>
         <v/>
@@ -7543,7 +7624,7 @@
       </c>
       <c r="R244" s="10"/>
     </row>
-    <row r="245" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="245" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M245" s="9" t="str" cm="1">
         <f t="array" ref="M245">PAGE_NAME(B245)</f>
         <v/>
@@ -7554,7 +7635,7 @@
       </c>
       <c r="R245" s="10"/>
     </row>
-    <row r="246" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="246" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M246" s="9" t="str" cm="1">
         <f t="array" ref="M246">PAGE_NAME(B246)</f>
         <v/>
@@ -7565,7 +7646,7 @@
       </c>
       <c r="R246" s="10"/>
     </row>
-    <row r="247" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="247" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M247" s="9" t="str" cm="1">
         <f t="array" ref="M247">PAGE_NAME(B247)</f>
         <v/>
@@ -7576,7 +7657,7 @@
       </c>
       <c r="R247" s="10"/>
     </row>
-    <row r="248" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="248" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M248" s="9" t="str" cm="1">
         <f t="array" ref="M248">PAGE_NAME(B248)</f>
         <v/>
@@ -7587,7 +7668,7 @@
       </c>
       <c r="R248" s="10"/>
     </row>
-    <row r="249" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="249" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M249" s="9" t="str" cm="1">
         <f t="array" ref="M249">PAGE_NAME(B249)</f>
         <v/>
@@ -7598,7 +7679,7 @@
       </c>
       <c r="R249" s="10"/>
     </row>
-    <row r="250" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="250" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M250" s="9" t="str" cm="1">
         <f t="array" ref="M250">PAGE_NAME(B250)</f>
         <v/>
@@ -7609,7 +7690,7 @@
       </c>
       <c r="R250" s="10"/>
     </row>
-    <row r="251" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="251" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M251" s="9" t="str" cm="1">
         <f t="array" ref="M251">PAGE_NAME(B251)</f>
         <v/>
@@ -7620,8 +7701,7 @@
       </c>
       <c r="R251" s="10"/>
     </row>
-    <row r="252" spans="2:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="B252" s="11"/>
+    <row r="252" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M252" s="9" t="str" cm="1">
         <f t="array" ref="M252">PAGE_NAME(B252)</f>
         <v/>
@@ -7632,7 +7712,7 @@
       </c>
       <c r="R252" s="10"/>
     </row>
-    <row r="253" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="253" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M253" s="9" t="str" cm="1">
         <f t="array" ref="M253">PAGE_NAME(B253)</f>
         <v/>
@@ -7643,7 +7723,7 @@
       </c>
       <c r="R253" s="10"/>
     </row>
-    <row r="254" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="254" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M254" s="9" t="str" cm="1">
         <f t="array" ref="M254">PAGE_NAME(B254)</f>
         <v/>
@@ -7654,7 +7734,7 @@
       </c>
       <c r="R254" s="10"/>
     </row>
-    <row r="255" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="255" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M255" s="9" t="str" cm="1">
         <f t="array" ref="M255">PAGE_NAME(B255)</f>
         <v/>
@@ -7665,7 +7745,7 @@
       </c>
       <c r="R255" s="10"/>
     </row>
-    <row r="256" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="13:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M256" s="9" t="str" cm="1">
         <f t="array" ref="M256">PAGE_NAME(B256)</f>
         <v/>
@@ -7676,7 +7756,8 @@
       </c>
       <c r="R256" s="10"/>
     </row>
-    <row r="257" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="2:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="B257" s="11"/>
       <c r="M257" s="9" t="str" cm="1">
         <f t="array" ref="M257">PAGE_NAME(B257)</f>
         <v/>
@@ -7687,7 +7768,7 @@
       </c>
       <c r="R257" s="10"/>
     </row>
-    <row r="258" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M258" s="9" t="str" cm="1">
         <f t="array" ref="M258">PAGE_NAME(B258)</f>
         <v/>
@@ -7698,7 +7779,7 @@
       </c>
       <c r="R258" s="10"/>
     </row>
-    <row r="259" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M259" s="9" t="str" cm="1">
         <f t="array" ref="M259">PAGE_NAME(B259)</f>
         <v/>
@@ -7709,7 +7790,7 @@
       </c>
       <c r="R259" s="10"/>
     </row>
-    <row r="260" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M260" s="9" t="str" cm="1">
         <f t="array" ref="M260">PAGE_NAME(B260)</f>
         <v/>
@@ -7720,7 +7801,7 @@
       </c>
       <c r="R260" s="10"/>
     </row>
-    <row r="261" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="261" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M261" s="9" t="str" cm="1">
         <f t="array" ref="M261">PAGE_NAME(B261)</f>
         <v/>
@@ -7731,7 +7812,7 @@
       </c>
       <c r="R261" s="10"/>
     </row>
-    <row r="262" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="262" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M262" s="9" t="str" cm="1">
         <f t="array" ref="M262">PAGE_NAME(B262)</f>
         <v/>
@@ -7742,7 +7823,7 @@
       </c>
       <c r="R262" s="10"/>
     </row>
-    <row r="263" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="263" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M263" s="9" t="str" cm="1">
         <f t="array" ref="M263">PAGE_NAME(B263)</f>
         <v/>
@@ -7753,7 +7834,7 @@
       </c>
       <c r="R263" s="10"/>
     </row>
-    <row r="264" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M264" s="9" t="str" cm="1">
         <f t="array" ref="M264">PAGE_NAME(B264)</f>
         <v/>
@@ -7764,7 +7845,7 @@
       </c>
       <c r="R264" s="10"/>
     </row>
-    <row r="265" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="265" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M265" s="9" t="str" cm="1">
         <f t="array" ref="M265">PAGE_NAME(B265)</f>
         <v/>
@@ -7775,7 +7856,7 @@
       </c>
       <c r="R265" s="10"/>
     </row>
-    <row r="266" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="266" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M266" s="9" t="str" cm="1">
         <f t="array" ref="M266">PAGE_NAME(B266)</f>
         <v/>
@@ -7786,7 +7867,7 @@
       </c>
       <c r="R266" s="10"/>
     </row>
-    <row r="267" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="267" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M267" s="9" t="str" cm="1">
         <f t="array" ref="M267">PAGE_NAME(B267)</f>
         <v/>
@@ -7797,7 +7878,7 @@
       </c>
       <c r="R267" s="10"/>
     </row>
-    <row r="268" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="268" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M268" s="9" t="str" cm="1">
         <f t="array" ref="M268">PAGE_NAME(B268)</f>
         <v/>
@@ -7808,7 +7889,7 @@
       </c>
       <c r="R268" s="10"/>
     </row>
-    <row r="269" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="269" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M269" s="9" t="str" cm="1">
         <f t="array" ref="M269">PAGE_NAME(B269)</f>
         <v/>
@@ -7819,7 +7900,7 @@
       </c>
       <c r="R269" s="10"/>
     </row>
-    <row r="270" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M270" s="9" t="str" cm="1">
         <f t="array" ref="M270">PAGE_NAME(B270)</f>
         <v/>
@@ -7830,7 +7911,7 @@
       </c>
       <c r="R270" s="10"/>
     </row>
-    <row r="271" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="271" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M271" s="9" t="str" cm="1">
         <f t="array" ref="M271">PAGE_NAME(B271)</f>
         <v/>
@@ -7841,7 +7922,7 @@
       </c>
       <c r="R271" s="10"/>
     </row>
-    <row r="272" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="2:18" ht="16" x14ac:dyDescent="0.2">
       <c r="M272" s="9" t="str" cm="1">
         <f t="array" ref="M272">PAGE_NAME(B272)</f>
         <v/>
@@ -8600,17 +8681,73 @@
       </c>
       <c r="R340" s="10"/>
     </row>
+    <row r="341" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="M341" s="9" t="str" cm="1">
+        <f t="array" ref="M341">PAGE_NAME(B341)</f>
+        <v/>
+      </c>
+      <c r="N341" s="9" t="str" cm="1">
+        <f t="array" ref="N341">SECTION_NAME(B341)</f>
+        <v/>
+      </c>
+      <c r="R341" s="10"/>
+    </row>
+    <row r="342" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="M342" s="9" t="str" cm="1">
+        <f t="array" ref="M342">PAGE_NAME(B342)</f>
+        <v/>
+      </c>
+      <c r="N342" s="9" t="str" cm="1">
+        <f t="array" ref="N342">SECTION_NAME(B342)</f>
+        <v/>
+      </c>
+      <c r="R342" s="10"/>
+    </row>
+    <row r="343" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="M343" s="9" t="str" cm="1">
+        <f t="array" ref="M343">PAGE_NAME(B343)</f>
+        <v/>
+      </c>
+      <c r="N343" s="9" t="str" cm="1">
+        <f t="array" ref="N343">SECTION_NAME(B343)</f>
+        <v/>
+      </c>
+      <c r="R343" s="10"/>
+    </row>
+    <row r="344" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="M344" s="9" t="str" cm="1">
+        <f t="array" ref="M344">PAGE_NAME(B344)</f>
+        <v/>
+      </c>
+      <c r="N344" s="9" t="str" cm="1">
+        <f t="array" ref="N344">SECTION_NAME(B344)</f>
+        <v/>
+      </c>
+      <c r="R344" s="10"/>
+    </row>
+    <row r="345" spans="13:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="M345" s="9" t="str" cm="1">
+        <f t="array" ref="M345">PAGE_NAME(B345)</f>
+        <v/>
+      </c>
+      <c r="N345" s="9" t="str" cm="1">
+        <f t="array" ref="N345">SECTION_NAME(B345)</f>
+        <v/>
+      </c>
+      <c r="R345" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AI340" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
+  <autoFilter ref="A1:AI345" xr:uid="{0272D98A-080C-3945-A7E0-CB54FB3A65A9}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B16" r:id="rId1" location="ci-c-conf-8" xr:uid="{FC667BFB-D838-C941-A847-F3F88E607223}"/>
-    <hyperlink ref="B76" r:id="rId2" location="ci-c-spec-35" xr:uid="{5FF64713-34D9-A748-A286-5A4D61DB8334}"/>
-    <hyperlink ref="B52" r:id="rId3" location="ci-c-spec-11" xr:uid="{4E0F9A5A-0897-2C4B-98E8-127D0E73D6C1}"/>
-    <hyperlink ref="B106" r:id="rId4" location="ci-c-spec-65" xr:uid="{2C76CA9A-AF34-C946-9996-4CD6012F10C0}"/>
-    <hyperlink ref="B67" r:id="rId5" location="ci-c-spec-26" xr:uid="{2791CF85-461B-1340-B643-634665A3629B}"/>
-    <hyperlink ref="B121" r:id="rId6" location="ci-c-conf-1" xr:uid="{F9502762-2CAC-054B-AC35-8FE364937A33}"/>
-    <hyperlink ref="B122" r:id="rId7" location="ci-c-conf-2" xr:uid="{B9020D2D-CDEC-9B45-9DBE-D41FF8F58455}"/>
+    <hyperlink ref="B81" r:id="rId2" location="ci-c-spec-35" xr:uid="{5FF64713-34D9-A748-A286-5A4D61DB8334}"/>
+    <hyperlink ref="B55" r:id="rId3" location="ci-c-spec-11" xr:uid="{4E0F9A5A-0897-2C4B-98E8-127D0E73D6C1}"/>
+    <hyperlink ref="B111" r:id="rId4" location="ci-c-spec-65" xr:uid="{2C76CA9A-AF34-C946-9996-4CD6012F10C0}"/>
+    <hyperlink ref="B72" r:id="rId5" location="ci-c-spec-26" xr:uid="{2791CF85-461B-1340-B643-634665A3629B}"/>
+    <hyperlink ref="B126" r:id="rId6" location="ci-c-conf-1" xr:uid="{F9502762-2CAC-054B-AC35-8FE364937A33}"/>
+    <hyperlink ref="B127" r:id="rId7" location="ci-c-conf-2" xr:uid="{B9020D2D-CDEC-9B45-9DBE-D41FF8F58455}"/>
+    <hyperlink ref="B93" r:id="rId8" location="ci-c-spec-47" xr:uid="{B7130BED-7461-0F46-838E-B72E3BE2BCC0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -8620,19 +8757,19 @@
           <x14:formula1>
             <xm:f>'Column Data'!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G224:G1048576 G1:G120 G154:G211</xm:sqref>
+          <xm:sqref>G229:G1048576 G159:G216 G1:G125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4866B9BF-5615-6646-965F-909D4D65F2A5}">
           <x14:formula1>
             <xm:f>'Column Data'!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D224:D1048576 D2:D211</xm:sqref>
+          <xm:sqref>D229:D1048576 D2:D216</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4FB27A2-804E-CB49-B85C-BBEE0C688B4F}">
           <x14:formula1>
             <xm:f>'Column Data'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>I224:I1048576 K224:K1048576 K2:K211 I2:I211</xm:sqref>
+          <xm:sqref>I229:I1048576 K229:K1048576 I2:I216 K2:K216</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8881,6 +9018,19 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -9134,19 +9284,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b5a44311-ed64-4a72-909f-c9dc6973bde2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Description xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-    <SortOrder xmlns="eebd8b74-b9de-41b2-9247-c010c4973c2b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
   <ds:schemaRefs>
@@ -9156,6 +9293,24 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
+    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12FB330C-B068-4EE3-928A-A72A297ABA91}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9173,22 +9328,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
-    <ds:schemaRef ds:uri="b7009bbd-f938-489b-a530-f05273710fff"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="b5a44311-ed64-4a72-909f-c9dc6973bde2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>